--- a/0_Threshold_OUTPUT/reverse_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/0_Threshold_OUTPUT/reverse_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.9098360655737705</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -586,6 +601,11 @@
       <c r="I4" t="n">
         <v>0.9824070371851259</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -664,6 +689,11 @@
       <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -703,6 +733,11 @@
       <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -742,6 +777,11 @@
       <c r="I8" t="n">
         <v>0.8188724510195922</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -781,6 +821,11 @@
       <c r="I9" t="n">
         <v>0.9962015193922431</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -820,6 +865,11 @@
       <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -859,6 +909,11 @@
       <c r="I11" t="n">
         <v>0.9976009596161536</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -898,6 +953,11 @@
       <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -937,6 +997,11 @@
       <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -976,6 +1041,11 @@
       <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1015,6 +1085,11 @@
       <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1054,6 +1129,11 @@
       <c r="I16" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1093,6 +1173,11 @@
       <c r="I17" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1132,6 +1217,11 @@
       <c r="I18" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1171,6 +1261,11 @@
       <c r="I19" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1210,6 +1305,11 @@
       <c r="I20" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1249,6 +1349,11 @@
       <c r="I21" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1288,6 +1393,11 @@
       <c r="I22" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1327,6 +1437,11 @@
       <c r="I23" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1366,6 +1481,11 @@
       <c r="I24" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1405,6 +1525,11 @@
       <c r="I25" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1444,6 +1569,11 @@
       <c r="I26" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1483,6 +1613,11 @@
       <c r="I27" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1522,6 +1657,11 @@
       <c r="I28" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1561,6 +1701,11 @@
       <c r="I29" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1600,6 +1745,11 @@
       <c r="I30" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1639,6 +1789,11 @@
       <c r="I31" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1678,6 +1833,11 @@
       <c r="I32" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1717,6 +1877,11 @@
       <c r="I33" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1756,6 +1921,11 @@
       <c r="I34" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1795,6 +1965,11 @@
       <c r="I35" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1834,6 +2009,11 @@
       <c r="I36" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1873,6 +2053,11 @@
       <c r="I37" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1912,6 +2097,11 @@
       <c r="I38" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1951,6 +2141,11 @@
       <c r="I39" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1990,6 +2185,11 @@
       <c r="I40" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2029,6 +2229,11 @@
       <c r="I41" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2068,6 +2273,11 @@
       <c r="I42" t="n">
         <v>0.9478208716513394</v>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2107,6 +2317,11 @@
       <c r="I43" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -2146,6 +2361,11 @@
       <c r="I44" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -2185,6 +2405,11 @@
       <c r="I45" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2224,6 +2449,11 @@
       <c r="I46" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -2262,6 +2492,11 @@
       </c>
       <c r="I47" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/0_Threshold_OUTPUT/reverse_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/0_Threshold_OUTPUT/reverse_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -606,6 +617,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -650,6 +664,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -694,6 +711,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -738,6 +758,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -782,6 +805,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -826,6 +852,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -870,6 +899,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -914,6 +946,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -958,6 +993,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1002,6 +1040,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1046,6 +1087,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1090,6 +1134,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1134,6 +1181,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1178,6 +1228,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1222,6 +1275,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1266,6 +1322,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1310,6 +1369,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1354,6 +1416,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1398,6 +1463,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1442,6 +1510,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1486,6 +1557,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K24" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1530,6 +1604,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1574,6 +1651,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1618,6 +1698,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1662,6 +1745,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1706,6 +1792,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1750,6 +1839,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1794,6 +1886,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1838,6 +1933,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K32" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1882,6 +1980,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K33" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1926,6 +2027,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K34" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1970,6 +2074,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2014,6 +2121,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2058,6 +2168,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2102,6 +2215,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K38" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2146,6 +2262,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K39" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2190,6 +2309,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K40" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2234,6 +2356,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K41" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2278,6 +2403,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K42" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2322,6 +2450,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K43" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -2366,6 +2497,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K44" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -2410,6 +2544,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K45" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2454,6 +2591,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K46" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -2497,6 +2637,9 @@
         <is>
           <t>Confirmed IR</t>
         </is>
+      </c>
+      <c r="K47" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
